--- a/gte/nodes/HPT/turbine_stage_1_blade_stator_coordinates_lattice.xlsx
+++ b/gte/nodes/HPT/turbine_stage_1_blade_stator_coordinates_lattice.xlsx
@@ -346,10 +346,10 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1">
-        <v>5.1946694610860655</v>
+        <v>5.20584881217977</v>
       </c>
       <c r="B1">
-        <v>29.537756526798326</v>
+        <v>29.528725634967167</v>
       </c>
       <c r="C1">
         <v>324.98254890622445</v>
@@ -357,10 +357,10 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2">
-        <v>7.5088519916245273</v>
+        <v>7.5181465469401836</v>
       </c>
       <c r="B2">
-        <v>26.430164432109464</v>
+        <v>26.421081512527248</v>
       </c>
       <c r="C2">
         <v>324.98254890622445</v>
@@ -368,10 +368,10 @@
     </row>
     <row r="3" spans="1:3">
       <c r="A3">
-        <v>8.47560497095789</v>
+        <v>8.483591439017566</v>
       </c>
       <c r="B3">
-        <v>24.018237147206882</v>
+        <v>24.009430574891994</v>
       </c>
       <c r="C3">
         <v>324.98254890622445</v>
@@ -379,10 +379,10 @@
     </row>
     <row r="4" spans="1:3">
       <c r="A4">
-        <v>9.1437681968685158</v>
+        <v>9.1505929748291024</v>
       </c>
       <c r="B4">
-        <v>21.760468856244419</v>
+        <v>21.752001787909421</v>
       </c>
       <c r="C4">
         <v>324.98254890622445</v>
@@ -390,10 +390,10 @@
     </row>
     <row r="5" spans="1:3">
       <c r="A5">
-        <v>9.6116973828171322</v>
+        <v>9.6174640035878074</v>
       </c>
       <c r="B5">
-        <v>19.606079458225427</v>
+        <v>19.597991477367675</v>
       </c>
       <c r="C5">
         <v>324.98254890622445</v>
@@ -401,10 +401,10 @@
     </row>
     <row r="6" spans="1:3">
       <c r="A6">
-        <v>9.92837662762563</v>
+        <v>9.9331652747718966</v>
       </c>
       <c r="B6">
-        <v>17.529778937980666</v>
+        <v>17.522098922297211</v>
       </c>
       <c r="C6">
         <v>324.98254890622445</v>
@@ -412,10 +412,10 @@
     </row>
     <row r="7" spans="1:3">
       <c r="A7">
-        <v>10.112204465022293</v>
+        <v>10.116086227597757</v>
       </c>
       <c r="B7">
-        <v>15.522068310976943</v>
+        <v>15.51482128470311</v>
       </c>
       <c r="C7">
         <v>324.98254890622445</v>
@@ -423,10 +423,10 @@
     </row>
     <row r="8" spans="1:3">
       <c r="A8">
-        <v>10.187887382187222</v>
+        <v>10.190920255360306</v>
       </c>
       <c r="B8">
-        <v>13.570191857489066</v>
+        <v>13.563398125658212</v>
       </c>
       <c r="C8">
         <v>324.98254890622445</v>
@@ -434,10 +434,10 @@
     </row>
     <row r="9" spans="1:3">
       <c r="A9">
-        <v>10.163338310614659</v>
+        <v>10.165575946234672</v>
       </c>
       <c r="B9">
-        <v>11.670064207726931</v>
+        <v>11.663742641246829</v>
       </c>
       <c r="C9">
         <v>324.98254890622445</v>
@@ -445,10 +445,10 @@
     </row>
     <row r="10" spans="1:3">
       <c r="A10">
-        <v>10.045449656600594</v>
+        <v>10.046941824871954</v>
       </c>
       <c r="B10">
-        <v>9.8181268791631222</v>
+        <v>9.8122951506645038</v>
       </c>
       <c r="C10">
         <v>324.98254890622445</v>
@@ -456,10 +456,10 @@
     </row>
     <row r="11" spans="1:3">
       <c r="A11">
-        <v>9.8403415954081179</v>
+        <v>9.8411345768532339</v>
       </c>
       <c r="B11">
-        <v>8.0112200846633623</v>
+        <v>8.00589482494529</v>
       </c>
       <c r="C11">
         <v>324.98254890622445</v>
@@ -467,10 +467,10 @@
     </row>
     <row r="12" spans="1:3">
       <c r="A12">
-        <v>9.5535143105951743</v>
+        <v>9.5536512434615037</v>
       </c>
       <c r="B12">
-        <v>6.2465041327979822</v>
+        <v>6.2417010395247887</v>
       </c>
       <c r="C12">
         <v>324.98254890622445</v>
@@ -478,10 +478,10 @@
     </row>
     <row r="13" spans="1:3">
       <c r="A13">
-        <v>9.1899441678981955</v>
+        <v>9.18946536332227</v>
       </c>
       <c r="B13">
-        <v>4.5214097741985428</v>
+        <v>4.5171436925492445</v>
       </c>
       <c r="C13">
         <v>324.98254890622445</v>
@@ -489,10 +489,10 @@
     </row>
     <row r="14" spans="1:3">
       <c r="A14">
-        <v>8.754148099496355</v>
+        <v>8.75309132977036</v>
       </c>
       <c r="B14">
-        <v>2.8336049605865754</v>
+        <v>2.829889947872803</v>
       </c>
       <c r="C14">
         <v>324.98254890622445</v>
@@ -500,10 +500,10 @@
     </row>
     <row r="15" spans="1:3">
       <c r="A15">
-        <v>8.25023115444066</v>
+        <v>8.2486319159401784</v>
       </c>
       <c r="B15">
-        <v>1.1809702949482013</v>
+        <v>1.1778196762208573</v>
       </c>
       <c r="C15">
         <v>324.98254890622445</v>
@@ -511,10 +511,10 @@
     </row>
     <row r="16" spans="1:3">
       <c r="A16">
-        <v>7.6819265473345659</v>
+        <v>7.6798182975489659</v>
       </c>
       <c r="B16">
-        <v>-0.43842164521126553</v>
+        <v>-0.44099522679052866</v>
       </c>
       <c r="C16">
         <v>324.98254890622445</v>
@@ -522,10 +522,10 @@
     </row>
     <row r="17" spans="1:3">
       <c r="A17">
-        <v>7.0526341102524919</v>
+        <v>7.05004847705497</v>
       </c>
       <c r="B17">
-        <v>-2.0263261602199565</v>
+        <v>-2.0283106965374773</v>
       </c>
       <c r="C17">
         <v>324.98254890622445</v>
@@ -533,10 +533,10 @@
     </row>
     <row r="18" spans="1:3">
       <c r="A18">
-        <v>6.36546096986928</v>
+        <v>6.3624279301712425</v>
       </c>
       <c r="B18">
-        <v>-3.5843474294468773</v>
+        <v>-3.5857315036848814</v>
       </c>
       <c r="C18">
         <v>324.98254890622445</v>
@@ -544,10 +544,10 @@
     </row>
     <row r="19" spans="1:3">
       <c r="A19">
-        <v>5.6039665383007</v>
+        <v>5.600524561360535</v>
       </c>
       <c r="B19">
-        <v>-5.103997336809794</v>
+        <v>-5.1047662777254681</v>
       </c>
       <c r="C19">
         <v>324.98254890622445</v>
@@ -555,10 +555,10 @@
     </row>
     <row r="20" spans="1:3">
       <c r="A20">
-        <v>4.7867603436399371</v>
+        <v>4.7829382923707522</v>
       </c>
       <c r="B20">
-        <v>-6.5948838011862376</v>
+        <v>-6.5950266245928626</v>
       </c>
       <c r="C20">
         <v>324.98254890622445</v>
@@ -566,10 +566,10 @@
     </row>
     <row r="21" spans="1:3">
       <c r="A21">
-        <v>3.9171873454579251</v>
+        <v>3.9130123942051256</v>
       </c>
       <c r="B21">
-        <v>-8.0587337927629346</v>
+        <v>-8.0582401969002184</v>
       </c>
       <c r="C21">
         <v>324.98254890622445</v>
@@ -577,10 +577,10 @@
     </row>
     <row r="22" spans="1:3">
       <c r="A22">
-        <v>2.9974594888669941</v>
+        <v>2.9929577079965135</v>
       </c>
       <c r="B22">
-        <v>-9.49668931734974</v>
+        <v>-9.495549458257809</v>
       </c>
       <c r="C22">
         <v>324.98254890622445</v>
@@ -588,10 +588,10 @@
     </row>
     <row r="23" spans="1:3">
       <c r="A23">
-        <v>2.0105763184140781</v>
+        <v>2.0057827455824944</v>
       </c>
       <c r="B23">
-        <v>-10.899973204668262</v>
+        <v>-10.898173969120981</v>
       </c>
       <c r="C23">
         <v>324.98254890622445</v>
@@ -599,10 +599,10 @@
     </row>
     <row r="24" spans="1:3">
       <c r="A24">
-        <v>0.9667489657953976</v>
+        <v>0.96169350605626769</v>
       </c>
       <c r="B24">
-        <v>-12.273857362984742</v>
+        <v>-12.271387732400712</v>
       </c>
       <c r="C24">
         <v>324.98254890622445</v>
@@ -610,10 +610,10 @@
     </row>
     <row r="25" spans="1:3">
       <c r="A25">
-        <v>-0.1241719799523807</v>
+        <v>-0.12946446421153307</v>
       </c>
       <c r="B25">
-        <v>-13.623427555886842</v>
+        <v>-13.620278485196037</v>
       </c>
       <c r="C25">
         <v>324.98254890622445</v>
@@ -621,10 +621,10 @@
     </row>
     <row r="26" spans="1:3">
       <c r="A26">
-        <v>-1.2642642271431508</v>
+        <v>-1.2697676836310214</v>
       </c>
       <c r="B26">
-        <v>-14.947611082721913</v>
+        <v>-14.943773175859597</v>
       </c>
       <c r="C26">
         <v>324.98254890622445</v>
@@ -632,10 +632,10 @@
     </row>
     <row r="27" spans="1:3">
       <c r="A27">
-        <v>-2.4793865113401483</v>
+        <v>-2.4850607319690479</v>
       </c>
       <c r="B27">
-        <v>-16.233057329099168</v>
+        <v>-16.22851648389031</v>
       </c>
       <c r="C27">
         <v>324.98254890622445</v>
@@ -643,10 +643,10 @@
     </row>
     <row r="28" spans="1:3">
       <c r="A28">
-        <v>-3.7403634408536677</v>
+        <v>-3.7461835293606622</v>
       </c>
       <c r="B28">
-        <v>-17.494829266802249</v>
+        <v>-17.489577031643311</v>
       </c>
       <c r="C28">
         <v>324.98254890622445</v>
@@ -654,10 +654,10 @@
     </row>
     <row r="29" spans="1:3">
       <c r="A29">
-        <v>-5.04588451564527</v>
+        <v>-5.05182620467792</v>
       </c>
       <c r="B29">
-        <v>-18.733603494291639</v>
+        <v>-18.727631701810719</v>
       </c>
       <c r="C29">
         <v>324.98254890622445</v>
@@ -665,10 +665,10 @@
     </row>
     <row r="30" spans="1:3">
       <c r="A30">
-        <v>-6.4293605010136785</v>
+        <v>-6.4353806751419222</v>
       </c>
       <c r="B30">
-        <v>-19.93213035746443</v>
+        <v>-19.925425048157468</v>
       </c>
       <c r="C30">
         <v>324.98254890622445</v>
@@ -676,10 +676,10 @@
     </row>
     <row r="31" spans="1:3">
       <c r="A31">
-        <v>-7.8651469047797073</v>
+        <v>-7.8712160207440078</v>
       </c>
       <c r="B31">
-        <v>-21.103649858929955</v>
+        <v>-21.096201981397609</v>
       </c>
       <c r="C31">
         <v>324.98254890622445</v>
@@ -687,10 +687,10 @@
     </row>
     <row r="32" spans="1:3">
       <c r="A32">
-        <v>-9.3463909710778</v>
+        <v>-9.352483206401363</v>
       </c>
       <c r="B32">
-        <v>-22.251700010082963</v>
+        <v>-22.243501775896583</v>
       </c>
       <c r="C32">
         <v>324.98254890622445</v>
@@ -698,10 +698,10 @@
     </row>
     <row r="33" spans="1:3">
       <c r="A33">
-        <v>-10.908943903270341</v>
+        <v>-10.915012177501808</v>
       </c>
       <c r="B33">
-        <v>-23.357771182315837</v>
+        <v>-23.348809121732216</v>
       </c>
       <c r="C33">
         <v>324.98254890622445</v>
@@ -709,10 +709,10 @@
     </row>
     <row r="34" spans="1:3">
       <c r="A34">
-        <v>-12.531456630552791</v>
+        <v>-12.537465182555593</v>
       </c>
       <c r="B34">
-        <v>-24.432885693839633</v>
+        <v>-24.423150412542533</v>
       </c>
       <c r="C34">
         <v>324.98254890622445</v>
@@ -720,10 +720,10 @@
     </row>
     <row r="35" spans="1:3">
       <c r="A35">
-        <v>-14.202464504244645</v>
+        <v>-14.208384175594929</v>
       </c>
       <c r="B35">
-        <v>-25.482962631582826</v>
+        <v>-25.472446652948104</v>
       </c>
       <c r="C35">
         <v>324.98254890622445</v>
@@ -731,10 +731,10 @@
     </row>
     <row r="36" spans="1:3">
       <c r="A36">
-        <v>-15.966791866082131</v>
+        <v>-15.972565016579285</v>
       </c>
       <c r="B36">
-        <v>-26.484859622617762</v>
+        <v>-26.473549350217425</v>
       </c>
       <c r="C36">
         <v>324.98254890622445</v>
@@ -742,10 +742,10 @@
     </row>
     <row r="37" spans="1:3">
       <c r="A37">
-        <v>-17.797555204414206</v>
+        <v>-17.803139063072919</v>
       </c>
       <c r="B37">
-        <v>-27.452456363291009</v>
+        <v>-27.440343014541661</v>
       </c>
       <c r="C37">
         <v>324.98254890622445</v>
@@ -753,10 +753,10 @@
     </row>
     <row r="38" spans="1:3">
       <c r="A38">
-        <v>-19.682688054455113</v>
+        <v>-19.688047368976878</v>
       </c>
       <c r="B38">
-        <v>-28.391982652349729</v>
+        <v>-28.379059168797564</v>
       </c>
       <c r="C38">
         <v>324.98254890622445</v>
@@ -764,10 +764,10 @@
     </row>
     <row r="39" spans="1:3">
       <c r="A39">
-        <v>-21.684247123249055</v>
+        <v>-21.689303160958378</v>
       </c>
       <c r="B39">
-        <v>-29.271399213778889</v>
+        <v>-29.257652156800351</v>
       </c>
       <c r="C39">
         <v>324.98254890622445</v>
@@ -775,10 +775,10 @@
     </row>
     <row r="40" spans="1:3">
       <c r="A40">
-        <v>-23.685806192042989</v>
+        <v>-23.690558952939881</v>
       </c>
       <c r="B40">
-        <v>-30.150815775208049</v>
+        <v>-30.136245144803137</v>
       </c>
       <c r="C40">
         <v>324.98254890622445</v>
@@ -786,10 +786,10 @@
     </row>
     <row r="41" spans="1:3">
       <c r="A41">
-        <v>-25.68736526083692</v>
+        <v>-25.69181474492137</v>
       </c>
       <c r="B41">
-        <v>-31.030232336637198</v>
+        <v>-31.01483813280592</v>
       </c>
       <c r="C41">
         <v>324.98254890622445</v>
@@ -797,10 +797,10 @@
     </row>
     <row r="42" spans="1:3">
       <c r="A42">
-        <v>-25.913292791802302</v>
+        <v>-25.917650762152356</v>
       </c>
       <c r="B42">
-        <v>-30.913588143466615</v>
+        <v>-30.898136200794493</v>
       </c>
       <c r="C42">
         <v>324.98254890622445</v>
@@ -808,10 +808,10 @@
     </row>
     <row r="43" spans="1:3">
       <c r="A43">
-        <v>-24.405990618049021</v>
+        <v>-24.410451662544638</v>
       </c>
       <c r="B43">
-        <v>-29.778991540478714</v>
+        <v>-29.764236857188461</v>
       </c>
       <c r="C43">
         <v>324.98254890622445</v>
@@ -819,10 +819,10 @@
     </row>
     <row r="44" spans="1:3">
       <c r="A44">
-        <v>-22.898688444295729</v>
+        <v>-22.90325256293691</v>
       </c>
       <c r="B44">
-        <v>-28.6443949374908</v>
+        <v>-28.630337513582425</v>
       </c>
       <c r="C44">
         <v>324.98254890622445</v>
@@ -830,10 +830,10 @@
     </row>
     <row r="45" spans="1:3">
       <c r="A45">
-        <v>-21.391386270542437</v>
+        <v>-21.396053463329185</v>
       </c>
       <c r="B45">
-        <v>-27.509798334502889</v>
+        <v>-27.49643816997639</v>
       </c>
       <c r="C45">
         <v>324.98254890622445</v>
@@ -841,10 +841,10 @@
     </row>
     <row r="46" spans="1:3">
       <c r="A46">
-        <v>-19.980169997276917</v>
+        <v>-19.984869770540627</v>
       </c>
       <c r="B46">
-        <v>-26.325593512943414</v>
+        <v>-26.312922367419088</v>
       </c>
       <c r="C46">
         <v>324.98254890622445</v>
@@ -852,10 +852,10 @@
     </row>
     <row r="47" spans="1:3">
       <c r="A47">
-        <v>-18.613544158376129</v>
+        <v>-18.618245220910968</v>
       </c>
       <c r="B47">
-        <v>-25.11836708256374</v>
+        <v>-25.106380396763452</v>
       </c>
       <c r="C47">
         <v>324.98254890622445</v>
@@ -863,10 +863,10 @@
     </row>
     <row r="48" spans="1:3">
       <c r="A48">
-        <v>-17.301348442987607</v>
+        <v>-17.306012886874022</v>
       </c>
       <c r="B48">
-        <v>-23.88303890728324</v>
+        <v>-23.871730966881962</v>
       </c>
       <c r="C48">
         <v>324.98254890622445</v>
@@ -874,10 +874,10 @@
     </row>
     <row r="49" spans="1:3">
       <c r="A49">
-        <v>-16.065004676267161</v>
+        <v>-16.06958193666965</v>
       </c>
       <c r="B49">
-        <v>-22.608549106524872</v>
+        <v>-22.597910779160927</v>
       </c>
       <c r="C49">
         <v>324.98254890622445</v>
@@ -885,10 +885,10 @@
     </row>
     <row r="50" spans="1:3">
       <c r="A50">
-        <v>-14.86779164701567</v>
+        <v>-14.872256358638323</v>
       </c>
       <c r="B50">
-        <v>-21.313856485504921</v>
+        <v>-21.303882687755713</v>
       </c>
       <c r="C50">
         <v>324.98254890622445</v>
@@ -896,10 +896,10 @@
     </row>
     <row r="51" spans="1:3">
       <c r="A51">
-        <v>-13.718855293630323</v>
+        <v>-13.723176427676478</v>
       </c>
       <c r="B51">
-        <v>-19.994239084927113</v>
+        <v>-19.984923408255778</v>
       </c>
       <c r="C51">
         <v>324.98254890622445</v>
@@ -907,10 +907,10 @@
     </row>
     <row r="52" spans="1:3">
       <c r="A52">
-        <v>-12.634611745046657</v>
+        <v>-12.638748951531994</v>
       </c>
       <c r="B52">
-        <v>-18.641221416627214</v>
+        <v>-18.63255463775003</v>
       </c>
       <c r="C52">
         <v>324.98254890622445</v>
@@ -918,10 +918,10 @@
     </row>
     <row r="53" spans="1:3">
       <c r="A53">
-        <v>-11.586121764439772</v>
+        <v>-11.590053151607803</v>
       </c>
       <c r="B53">
-        <v>-17.269744527922445</v>
+        <v>-17.261721338423573</v>
       </c>
       <c r="C53">
         <v>324.98254890622445</v>
@@ -929,10 +929,10 @@
     </row>
     <row r="54" spans="1:3">
       <c r="A54">
-        <v>-10.578632365700374</v>
+        <v>-10.582332971430349</v>
       </c>
       <c r="B54">
-        <v>-15.877099436427047</v>
+        <v>-15.869713675289068</v>
       </c>
       <c r="C54">
         <v>324.98254890622445</v>
@@ -940,10 +940,10 @@
     </row>
     <row r="55" spans="1:3">
       <c r="A55">
-        <v>-9.6311101925546136</v>
+        <v>-9.6345441874706275</v>
       </c>
       <c r="B55">
-        <v>-14.453493847925564</v>
+        <v>-14.44673615264097</v>
       </c>
       <c r="C55">
         <v>324.98254890622445</v>
@@ -951,10 +951,10 @@
     </row>
     <row r="56" spans="1:3">
       <c r="A56">
-        <v>-8.717178369031032</v>
+        <v>-8.720325922702262</v>
       </c>
       <c r="B56">
-        <v>-13.012545887676572</v>
+        <v>-13.006410890264315</v>
       </c>
       <c r="C56">
         <v>324.98254890622445</v>
@@ -962,10 +962,10 @@
     </row>
     <row r="57" spans="1:3">
       <c r="A57">
-        <v>-7.8376460711809779</v>
+        <v>-7.8404869273313649</v>
       </c>
       <c r="B57">
-        <v>-11.553837785932235</v>
+        <v>-11.548319962299768</v>
       </c>
       <c r="C57">
         <v>324.98254890622445</v>
@@ -973,10 +973,10 @@
     </row>
     <row r="58" spans="1:3">
       <c r="A58">
-        <v>-7.0129989394386367</v>
+        <v>-7.0155010498198669</v>
       </c>
       <c r="B58">
-        <v>-10.066793005208101</v>
+        <v>-10.06188340147502</v>
       </c>
       <c r="C58">
         <v>324.98254890622445</v>
@@ -984,10 +984,10 @@
     </row>
     <row r="59" spans="1:3">
       <c r="A59">
-        <v>-6.2231833424116836</v>
+        <v>-6.225326463168452</v>
       </c>
       <c r="B59">
-        <v>-8.5617650409099664</v>
+        <v>-8.5574579257331642</v>
       </c>
       <c r="C59">
         <v>324.98254890622445</v>
@@ -995,10 +995,10 @@
     </row>
     <row r="60" spans="1:3">
       <c r="A60">
-        <v>-5.4662358834241251</v>
+        <v>-5.4680009143020749</v>
       </c>
       <c r="B60">
-        <v>-7.039767575700437</v>
+        <v>-7.0360575395176284</v>
       </c>
       <c r="C60">
         <v>324.98254890622445</v>
@@ -1006,10 +1006,10 @@
     </row>
     <row r="61" spans="1:3">
       <c r="A61">
-        <v>-4.7481606647278669</v>
+        <v>-4.7495250208565158</v>
       </c>
       <c r="B61">
-        <v>-5.4977007498152286</v>
+        <v>-5.4945813925745526</v>
       </c>
       <c r="C61">
         <v>324.98254890622445</v>
@@ -1017,10 +1017,10 @@
     </row>
     <row r="62" spans="1:3">
       <c r="A62">
-        <v>-4.0740451396258752</v>
+        <v>-4.0749831789182025</v>
       </c>
       <c r="B62">
-        <v>-3.9329379604526142</v>
+        <v>-3.9304020968828928</v>
       </c>
       <c r="C62">
         <v>324.98254890622445</v>
@@ -1028,10 +1028,10 @@
     </row>
     <row r="63" spans="1:3">
       <c r="A63">
-        <v>-3.4315013189186865</v>
+        <v>-3.4319944982623656</v>
       </c>
       <c r="B63">
-        <v>-2.3518750062963836</v>
+        <v>-2.3499175416144693</v>
       </c>
       <c r="C63">
         <v>324.98254890622445</v>
@@ -1039,10 +1039,10 @@
     </row>
     <row r="64" spans="1:3">
       <c r="A64">
-        <v>-2.8210533640799773</v>
+        <v>-2.8210827200333157</v>
       </c>
       <c r="B64">
-        <v>-0.75424126786103818</v>
+        <v>-0.75285708081933755</v>
       </c>
       <c r="C64">
         <v>324.98254890622445</v>
@@ -1050,10 +1050,10 @@
     </row>
     <row r="65" spans="1:3">
       <c r="A65">
-        <v>-2.2436372701372962</v>
+        <v>-2.2431831264610564</v>
       </c>
       <c r="B65">
-        <v>0.8604465000087711</v>
+        <v>0.8612625974407575</v>
       </c>
       <c r="C65">
         <v>324.98254890622445</v>
@@ -1061,10 +1061,10 @@
     </row>
     <row r="66" spans="1:3">
       <c r="A66">
-        <v>-1.7078319836856812</v>
+        <v>-1.7068691207617752</v>
       </c>
       <c r="B66">
-        <v>2.496617524240623</v>
+        <v>2.4968718436985236</v>
       </c>
       <c r="C66">
         <v>324.98254890622445</v>
@@ -1072,10 +1072,10 @@
     </row>
     <row r="67" spans="1:3">
       <c r="A67">
-        <v>-1.2024885217635939</v>
+        <v>-1.2009980689144464</v>
       </c>
       <c r="B67">
-        <v>4.1485156930553764</v>
+        <v>4.14821264409109</v>
       </c>
       <c r="C67">
         <v>324.98254890622445</v>
@@ -1083,10 +1083,10 @@
     </row>
     <row r="68" spans="1:3">
       <c r="A68">
-        <v>-0.72772747371769142</v>
+        <v>-0.72569011902452485</v>
       </c>
       <c r="B68">
-        <v>5.81620326556322</v>
+        <v>5.8153470857744658</v>
       </c>
       <c r="C68">
         <v>324.98254890622445</v>
@@ -1094,10 +1094,10 @@
     </row>
     <row r="69" spans="1:3">
       <c r="A69">
-        <v>-0.28347115476825768</v>
+        <v>-0.28086716529184941</v>
       </c>
       <c r="B69">
-        <v>7.4996401338657872</v>
+        <v>7.4982348071717411</v>
       </c>
       <c r="C69">
         <v>324.98254890622445</v>
@@ -1105,10 +1105,10 @@
     </row>
     <row r="70" spans="1:3">
       <c r="A70">
-        <v>0.13059338895845618</v>
+        <v>0.13378414611098666</v>
       </c>
       <c r="B70">
-        <v>9.1986647229131133</v>
+        <v>9.1967138810690372</v>
       </c>
       <c r="C70">
         <v>324.98254890622445</v>
@@ -1116,10 +1116,10 @@
     </row>
     <row r="71" spans="1:3">
       <c r="A71">
-        <v>0.51506797532148774</v>
+        <v>0.51886600240592762</v>
       </c>
       <c r="B71">
-        <v>10.912966319981067</v>
+        <v>10.910473124099356</v>
       </c>
       <c r="C71">
         <v>324.98254890622445</v>
@@ -1127,10 +1127,10 @@
     </row>
     <row r="72" spans="1:3">
       <c r="A72">
-        <v>0.87091986704142255</v>
+        <v>0.8753459837413623</v>
       </c>
       <c r="B72">
-        <v>12.64204553670762</v>
+        <v>12.639012534207762</v>
       </c>
       <c r="C72">
         <v>324.98254890622445</v>
@@ -1138,10 +1138,10 @@
     </row>
     <row r="73" spans="1:3">
       <c r="A73">
-        <v>1.1995907764463398</v>
+        <v>1.204666029862981</v>
       </c>
       <c r="B73">
-        <v>14.385158030999643</v>
+        <v>14.381586981559652</v>
       </c>
       <c r="C73">
         <v>324.98254890622445</v>
@@ -1149,10 +1149,10 @@
     </row>
     <row r="74" spans="1:3">
       <c r="A74">
-        <v>1.5031519570210434</v>
+        <v>1.50889746966005</v>
       </c>
       <c r="B74">
-        <v>16.141234434770148</v>
+        <v>16.137126096219479</v>
       </c>
       <c r="C74">
         <v>324.98254890622445</v>
@@ -1160,10 +1160,10 @@
     </row>
     <row r="75" spans="1:3">
       <c r="A75">
-        <v>1.7845252050094334</v>
+        <v>1.7909619265363534</v>
       </c>
       <c r="B75">
-        <v>17.908766252954265</v>
+        <v>17.904120114155742</v>
       </c>
       <c r="C75">
         <v>324.98254890622445</v>
@@ -1171,10 +1171,10 @@
     </row>
     <row r="76" spans="1:3">
       <c r="A76">
-        <v>2.0477990420384589</v>
+        <v>2.0549473558519771</v>
       </c>
       <c r="B76">
-        <v>19.685642621486885</v>
+        <v>19.680456563255508</v>
       </c>
       <c r="C76">
         <v>324.98254890622445</v>
@@ -1182,10 +1182,10 @@
     </row>
     <row r="77" spans="1:3">
       <c r="A77">
-        <v>2.2986845766583519</v>
+        <v>2.3065636909510308</v>
       </c>
       <c r="B77">
-        <v>21.4689149504104</v>
+        <v>21.463184805878758</v>
       </c>
       <c r="C77">
         <v>324.98254890622445</v>
@@ -1193,10 +1193,10 @@
     </row>
     <row r="78" spans="1:3">
       <c r="A78">
-        <v>2.5461274351130023</v>
+        <v>2.5547560209077158</v>
       </c>
       <c r="B78">
-        <v>23.253964699650616</v>
+        <v>23.247682420899864</v>
       </c>
       <c r="C78">
         <v>324.98254890622445</v>
@@ -1204,10 +1204,10 @@
     </row>
     <row r="79" spans="1:3">
       <c r="A79">
-        <v>2.80653912859926</v>
+        <v>2.8159308513466</v>
       </c>
       <c r="B79">
-        <v>25.032318765137031</v>
+        <v>25.025471261531525</v>
       </c>
       <c r="C79">
         <v>324.98254890622445</v>
@@ -1215,10 +1215,10 @@
     </row>
     <row r="80" spans="1:3">
       <c r="A80">
-        <v>3.116639554003457</v>
+        <v>3.12679671341597</v>
       </c>
       <c r="B80">
-        <v>26.78501902022029</v>
+        <v>26.777582004107703</v>
       </c>
       <c r="C80">
         <v>324.98254890622445</v>
@@ -1226,10 +1226,10 @@
     </row>
     <row r="81" spans="1:3">
       <c r="A81">
-        <v>3.56868724380857</v>
+        <v>3.5795777940376796</v>
       </c>
       <c r="B81">
-        <v>28.464433279311528</v>
+        <v>28.456357322202226</v>
       </c>
       <c r="C81">
         <v>324.98254890622445</v>
@@ -1237,10 +1237,10 @@
     </row>
     <row r="82" spans="1:3">
       <c r="A82">
-        <v>5.1946694610860655</v>
+        <v>5.20584881217977</v>
       </c>
       <c r="B82">
-        <v>29.537756526798326</v>
+        <v>29.528725634967167</v>
       </c>
       <c r="C82">
         <v>324.98254890622445</v>
@@ -1258,10 +1258,10 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1">
-        <v>5.1946694610860655</v>
+        <v>5.20584881217977</v>
       </c>
       <c r="B1">
-        <v>29.537756526798326</v>
+        <v>29.528725634967167</v>
       </c>
       <c r="C1">
         <v>339.231271826982</v>
@@ -1269,10 +1269,10 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2">
-        <v>7.5088519916245273</v>
+        <v>7.5181465469401836</v>
       </c>
       <c r="B2">
-        <v>26.430164432109464</v>
+        <v>26.421081512527248</v>
       </c>
       <c r="C2">
         <v>339.231271826982</v>
@@ -1280,10 +1280,10 @@
     </row>
     <row r="3" spans="1:3">
       <c r="A3">
-        <v>8.47560497095789</v>
+        <v>8.483591439017566</v>
       </c>
       <c r="B3">
-        <v>24.018237147206882</v>
+        <v>24.009430574891994</v>
       </c>
       <c r="C3">
         <v>339.231271826982</v>
@@ -1291,10 +1291,10 @@
     </row>
     <row r="4" spans="1:3">
       <c r="A4">
-        <v>9.1437681968685158</v>
+        <v>9.1505929748291024</v>
       </c>
       <c r="B4">
-        <v>21.760468856244419</v>
+        <v>21.752001787909421</v>
       </c>
       <c r="C4">
         <v>339.231271826982</v>
@@ -1302,10 +1302,10 @@
     </row>
     <row r="5" spans="1:3">
       <c r="A5">
-        <v>9.6116973828171322</v>
+        <v>9.6174640035878074</v>
       </c>
       <c r="B5">
-        <v>19.606079458225427</v>
+        <v>19.597991477367675</v>
       </c>
       <c r="C5">
         <v>339.231271826982</v>
@@ -1313,10 +1313,10 @@
     </row>
     <row r="6" spans="1:3">
       <c r="A6">
-        <v>9.92837662762563</v>
+        <v>9.9331652747718966</v>
       </c>
       <c r="B6">
-        <v>17.529778937980666</v>
+        <v>17.522098922297211</v>
       </c>
       <c r="C6">
         <v>339.231271826982</v>
@@ -1324,10 +1324,10 @@
     </row>
     <row r="7" spans="1:3">
       <c r="A7">
-        <v>10.112204465022293</v>
+        <v>10.116086227597757</v>
       </c>
       <c r="B7">
-        <v>15.522068310976943</v>
+        <v>15.51482128470311</v>
       </c>
       <c r="C7">
         <v>339.231271826982</v>
@@ -1335,10 +1335,10 @@
     </row>
     <row r="8" spans="1:3">
       <c r="A8">
-        <v>10.187887382187222</v>
+        <v>10.190920255360306</v>
       </c>
       <c r="B8">
-        <v>13.570191857489066</v>
+        <v>13.563398125658212</v>
       </c>
       <c r="C8">
         <v>339.231271826982</v>
@@ -1346,10 +1346,10 @@
     </row>
     <row r="9" spans="1:3">
       <c r="A9">
-        <v>10.163338310614659</v>
+        <v>10.165575946234672</v>
       </c>
       <c r="B9">
-        <v>11.670064207726931</v>
+        <v>11.663742641246829</v>
       </c>
       <c r="C9">
         <v>339.231271826982</v>
@@ -1357,10 +1357,10 @@
     </row>
     <row r="10" spans="1:3">
       <c r="A10">
-        <v>10.045449656600594</v>
+        <v>10.046941824871954</v>
       </c>
       <c r="B10">
-        <v>9.8181268791631222</v>
+        <v>9.8122951506645038</v>
       </c>
       <c r="C10">
         <v>339.231271826982</v>
@@ -1368,10 +1368,10 @@
     </row>
     <row r="11" spans="1:3">
       <c r="A11">
-        <v>9.8403415954081179</v>
+        <v>9.8411345768532339</v>
       </c>
       <c r="B11">
-        <v>8.0112200846633623</v>
+        <v>8.00589482494529</v>
       </c>
       <c r="C11">
         <v>339.231271826982</v>
@@ -1379,10 +1379,10 @@
     </row>
     <row r="12" spans="1:3">
       <c r="A12">
-        <v>9.5535143105951743</v>
+        <v>9.5536512434615037</v>
       </c>
       <c r="B12">
-        <v>6.2465041327979822</v>
+        <v>6.2417010395247887</v>
       </c>
       <c r="C12">
         <v>339.231271826982</v>
@@ -1390,10 +1390,10 @@
     </row>
     <row r="13" spans="1:3">
       <c r="A13">
-        <v>9.1899441678981955</v>
+        <v>9.18946536332227</v>
       </c>
       <c r="B13">
-        <v>4.5214097741985428</v>
+        <v>4.5171436925492445</v>
       </c>
       <c r="C13">
         <v>339.231271826982</v>
@@ -1401,10 +1401,10 @@
     </row>
     <row r="14" spans="1:3">
       <c r="A14">
-        <v>8.754148099496355</v>
+        <v>8.75309132977036</v>
       </c>
       <c r="B14">
-        <v>2.8336049605865754</v>
+        <v>2.829889947872803</v>
       </c>
       <c r="C14">
         <v>339.231271826982</v>
@@ -1412,10 +1412,10 @@
     </row>
     <row r="15" spans="1:3">
       <c r="A15">
-        <v>8.25023115444066</v>
+        <v>8.2486319159401784</v>
       </c>
       <c r="B15">
-        <v>1.1809702949482013</v>
+        <v>1.1778196762208573</v>
       </c>
       <c r="C15">
         <v>339.231271826982</v>
@@ -1423,10 +1423,10 @@
     </row>
     <row r="16" spans="1:3">
       <c r="A16">
-        <v>7.6819265473345659</v>
+        <v>7.6798182975489659</v>
       </c>
       <c r="B16">
-        <v>-0.43842164521126553</v>
+        <v>-0.44099522679052866</v>
       </c>
       <c r="C16">
         <v>339.231271826982</v>
@@ -1434,10 +1434,10 @@
     </row>
     <row r="17" spans="1:3">
       <c r="A17">
-        <v>7.0526341102524919</v>
+        <v>7.05004847705497</v>
       </c>
       <c r="B17">
-        <v>-2.0263261602199565</v>
+        <v>-2.0283106965374773</v>
       </c>
       <c r="C17">
         <v>339.231271826982</v>
@@ -1445,10 +1445,10 @@
     </row>
     <row r="18" spans="1:3">
       <c r="A18">
-        <v>6.36546096986928</v>
+        <v>6.3624279301712425</v>
       </c>
       <c r="B18">
-        <v>-3.5843474294468773</v>
+        <v>-3.5857315036848814</v>
       </c>
       <c r="C18">
         <v>339.231271826982</v>
@@ -1456,10 +1456,10 @@
     </row>
     <row r="19" spans="1:3">
       <c r="A19">
-        <v>5.6039665383007</v>
+        <v>5.600524561360535</v>
       </c>
       <c r="B19">
-        <v>-5.103997336809794</v>
+        <v>-5.1047662777254681</v>
       </c>
       <c r="C19">
         <v>339.231271826982</v>
@@ -1467,10 +1467,10 @@
     </row>
     <row r="20" spans="1:3">
       <c r="A20">
-        <v>4.7867603436399371</v>
+        <v>4.7829382923707522</v>
       </c>
       <c r="B20">
-        <v>-6.5948838011862376</v>
+        <v>-6.5950266245928626</v>
       </c>
       <c r="C20">
         <v>339.231271826982</v>
@@ -1478,10 +1478,10 @@
     </row>
     <row r="21" spans="1:3">
       <c r="A21">
-        <v>3.9171873454579251</v>
+        <v>3.9130123942051256</v>
       </c>
       <c r="B21">
-        <v>-8.0587337927629346</v>
+        <v>-8.0582401969002184</v>
       </c>
       <c r="C21">
         <v>339.231271826982</v>
@@ -1489,10 +1489,10 @@
     </row>
     <row r="22" spans="1:3">
       <c r="A22">
-        <v>2.9974594888669941</v>
+        <v>2.9929577079965135</v>
       </c>
       <c r="B22">
-        <v>-9.49668931734974</v>
+        <v>-9.495549458257809</v>
       </c>
       <c r="C22">
         <v>339.231271826982</v>
@@ -1500,10 +1500,10 @@
     </row>
     <row r="23" spans="1:3">
       <c r="A23">
-        <v>2.0105763184140781</v>
+        <v>2.0057827455824944</v>
       </c>
       <c r="B23">
-        <v>-10.899973204668262</v>
+        <v>-10.898173969120981</v>
       </c>
       <c r="C23">
         <v>339.231271826982</v>
@@ -1511,10 +1511,10 @@
     </row>
     <row r="24" spans="1:3">
       <c r="A24">
-        <v>0.9667489657953976</v>
+        <v>0.96169350605626769</v>
       </c>
       <c r="B24">
-        <v>-12.273857362984742</v>
+        <v>-12.271387732400712</v>
       </c>
       <c r="C24">
         <v>339.231271826982</v>
@@ -1522,10 +1522,10 @@
     </row>
     <row r="25" spans="1:3">
       <c r="A25">
-        <v>-0.1241719799523807</v>
+        <v>-0.12946446421153307</v>
       </c>
       <c r="B25">
-        <v>-13.623427555886842</v>
+        <v>-13.620278485196037</v>
       </c>
       <c r="C25">
         <v>339.231271826982</v>
@@ -1533,10 +1533,10 @@
     </row>
     <row r="26" spans="1:3">
       <c r="A26">
-        <v>-1.2642642271431508</v>
+        <v>-1.2697676836310214</v>
       </c>
       <c r="B26">
-        <v>-14.947611082721913</v>
+        <v>-14.943773175859597</v>
       </c>
       <c r="C26">
         <v>339.231271826982</v>
@@ -1544,10 +1544,10 @@
     </row>
     <row r="27" spans="1:3">
       <c r="A27">
-        <v>-2.4793865113401483</v>
+        <v>-2.4850607319690479</v>
       </c>
       <c r="B27">
-        <v>-16.233057329099168</v>
+        <v>-16.22851648389031</v>
       </c>
       <c r="C27">
         <v>339.231271826982</v>
@@ -1555,10 +1555,10 @@
     </row>
     <row r="28" spans="1:3">
       <c r="A28">
-        <v>-3.7403634408536677</v>
+        <v>-3.7461835293606622</v>
       </c>
       <c r="B28">
-        <v>-17.494829266802249</v>
+        <v>-17.489577031643311</v>
       </c>
       <c r="C28">
         <v>339.231271826982</v>
@@ -1566,10 +1566,10 @@
     </row>
     <row r="29" spans="1:3">
       <c r="A29">
-        <v>-5.04588451564527</v>
+        <v>-5.05182620467792</v>
       </c>
       <c r="B29">
-        <v>-18.733603494291639</v>
+        <v>-18.727631701810719</v>
       </c>
       <c r="C29">
         <v>339.231271826982</v>
@@ -1577,10 +1577,10 @@
     </row>
     <row r="30" spans="1:3">
       <c r="A30">
-        <v>-6.4293605010136785</v>
+        <v>-6.4353806751419222</v>
       </c>
       <c r="B30">
-        <v>-19.93213035746443</v>
+        <v>-19.925425048157468</v>
       </c>
       <c r="C30">
         <v>339.231271826982</v>
@@ -1588,10 +1588,10 @@
     </row>
     <row r="31" spans="1:3">
       <c r="A31">
-        <v>-7.8651469047797073</v>
+        <v>-7.8712160207440078</v>
       </c>
       <c r="B31">
-        <v>-21.103649858929955</v>
+        <v>-21.096201981397609</v>
       </c>
       <c r="C31">
         <v>339.231271826982</v>
@@ -1599,10 +1599,10 @@
     </row>
     <row r="32" spans="1:3">
       <c r="A32">
-        <v>-9.3463909710778</v>
+        <v>-9.352483206401363</v>
       </c>
       <c r="B32">
-        <v>-22.251700010082963</v>
+        <v>-22.243501775896583</v>
       </c>
       <c r="C32">
         <v>339.231271826982</v>
@@ -1610,10 +1610,10 @@
     </row>
     <row r="33" spans="1:3">
       <c r="A33">
-        <v>-10.908943903270341</v>
+        <v>-10.915012177501808</v>
       </c>
       <c r="B33">
-        <v>-23.357771182315837</v>
+        <v>-23.348809121732216</v>
       </c>
       <c r="C33">
         <v>339.231271826982</v>
@@ -1621,10 +1621,10 @@
     </row>
     <row r="34" spans="1:3">
       <c r="A34">
-        <v>-12.531456630552791</v>
+        <v>-12.537465182555593</v>
       </c>
       <c r="B34">
-        <v>-24.432885693839633</v>
+        <v>-24.423150412542533</v>
       </c>
       <c r="C34">
         <v>339.231271826982</v>
@@ -1632,10 +1632,10 @@
     </row>
     <row r="35" spans="1:3">
       <c r="A35">
-        <v>-14.202464504244645</v>
+        <v>-14.208384175594929</v>
       </c>
       <c r="B35">
-        <v>-25.482962631582826</v>
+        <v>-25.472446652948104</v>
       </c>
       <c r="C35">
         <v>339.231271826982</v>
@@ -1643,10 +1643,10 @@
     </row>
     <row r="36" spans="1:3">
       <c r="A36">
-        <v>-15.966791866082131</v>
+        <v>-15.972565016579285</v>
       </c>
       <c r="B36">
-        <v>-26.484859622617762</v>
+        <v>-26.473549350217425</v>
       </c>
       <c r="C36">
         <v>339.231271826982</v>
@@ -1654,10 +1654,10 @@
     </row>
     <row r="37" spans="1:3">
       <c r="A37">
-        <v>-17.797555204414206</v>
+        <v>-17.803139063072919</v>
       </c>
       <c r="B37">
-        <v>-27.452456363291009</v>
+        <v>-27.440343014541661</v>
       </c>
       <c r="C37">
         <v>339.231271826982</v>
@@ -1665,10 +1665,10 @@
     </row>
     <row r="38" spans="1:3">
       <c r="A38">
-        <v>-19.682688054455113</v>
+        <v>-19.688047368976878</v>
       </c>
       <c r="B38">
-        <v>-28.391982652349729</v>
+        <v>-28.379059168797564</v>
       </c>
       <c r="C38">
         <v>339.231271826982</v>
@@ -1676,10 +1676,10 @@
     </row>
     <row r="39" spans="1:3">
       <c r="A39">
-        <v>-21.684247123249055</v>
+        <v>-21.689303160958378</v>
       </c>
       <c r="B39">
-        <v>-29.271399213778889</v>
+        <v>-29.257652156800351</v>
       </c>
       <c r="C39">
         <v>339.231271826982</v>
@@ -1687,10 +1687,10 @@
     </row>
     <row r="40" spans="1:3">
       <c r="A40">
-        <v>-23.685806192042989</v>
+        <v>-23.690558952939881</v>
       </c>
       <c r="B40">
-        <v>-30.150815775208049</v>
+        <v>-30.136245144803137</v>
       </c>
       <c r="C40">
         <v>339.231271826982</v>
@@ -1698,10 +1698,10 @@
     </row>
     <row r="41" spans="1:3">
       <c r="A41">
-        <v>-25.68736526083692</v>
+        <v>-25.69181474492137</v>
       </c>
       <c r="B41">
-        <v>-31.030232336637198</v>
+        <v>-31.01483813280592</v>
       </c>
       <c r="C41">
         <v>339.231271826982</v>
@@ -1709,10 +1709,10 @@
     </row>
     <row r="42" spans="1:3">
       <c r="A42">
-        <v>-25.913292791802302</v>
+        <v>-25.917650762152356</v>
       </c>
       <c r="B42">
-        <v>-30.913588143466615</v>
+        <v>-30.898136200794493</v>
       </c>
       <c r="C42">
         <v>339.231271826982</v>
@@ -1720,10 +1720,10 @@
     </row>
     <row r="43" spans="1:3">
       <c r="A43">
-        <v>-24.405990618049021</v>
+        <v>-24.410451662544638</v>
       </c>
       <c r="B43">
-        <v>-29.778991540478714</v>
+        <v>-29.764236857188461</v>
       </c>
       <c r="C43">
         <v>339.231271826982</v>
@@ -1731,10 +1731,10 @@
     </row>
     <row r="44" spans="1:3">
       <c r="A44">
-        <v>-22.898688444295729</v>
+        <v>-22.90325256293691</v>
       </c>
       <c r="B44">
-        <v>-28.6443949374908</v>
+        <v>-28.630337513582425</v>
       </c>
       <c r="C44">
         <v>339.231271826982</v>
@@ -1742,10 +1742,10 @@
     </row>
     <row r="45" spans="1:3">
       <c r="A45">
-        <v>-21.391386270542437</v>
+        <v>-21.396053463329185</v>
       </c>
       <c r="B45">
-        <v>-27.509798334502889</v>
+        <v>-27.49643816997639</v>
       </c>
       <c r="C45">
         <v>339.231271826982</v>
@@ -1753,10 +1753,10 @@
     </row>
     <row r="46" spans="1:3">
       <c r="A46">
-        <v>-19.980169997276917</v>
+        <v>-19.984869770540627</v>
       </c>
       <c r="B46">
-        <v>-26.325593512943414</v>
+        <v>-26.312922367419088</v>
       </c>
       <c r="C46">
         <v>339.231271826982</v>
@@ -1764,10 +1764,10 @@
     </row>
     <row r="47" spans="1:3">
       <c r="A47">
-        <v>-18.613544158376129</v>
+        <v>-18.618245220910968</v>
       </c>
       <c r="B47">
-        <v>-25.11836708256374</v>
+        <v>-25.106380396763452</v>
       </c>
       <c r="C47">
         <v>339.231271826982</v>
@@ -1775,10 +1775,10 @@
     </row>
     <row r="48" spans="1:3">
       <c r="A48">
-        <v>-17.301348442987607</v>
+        <v>-17.306012886874022</v>
       </c>
       <c r="B48">
-        <v>-23.88303890728324</v>
+        <v>-23.871730966881962</v>
       </c>
       <c r="C48">
         <v>339.231271826982</v>
@@ -1786,10 +1786,10 @@
     </row>
     <row r="49" spans="1:3">
       <c r="A49">
-        <v>-16.065004676267161</v>
+        <v>-16.06958193666965</v>
       </c>
       <c r="B49">
-        <v>-22.608549106524872</v>
+        <v>-22.597910779160927</v>
       </c>
       <c r="C49">
         <v>339.231271826982</v>
@@ -1797,10 +1797,10 @@
     </row>
     <row r="50" spans="1:3">
       <c r="A50">
-        <v>-14.86779164701567</v>
+        <v>-14.872256358638323</v>
       </c>
       <c r="B50">
-        <v>-21.313856485504921</v>
+        <v>-21.303882687755713</v>
       </c>
       <c r="C50">
         <v>339.231271826982</v>
@@ -1808,10 +1808,10 @@
     </row>
     <row r="51" spans="1:3">
       <c r="A51">
-        <v>-13.718855293630323</v>
+        <v>-13.723176427676478</v>
       </c>
       <c r="B51">
-        <v>-19.994239084927113</v>
+        <v>-19.984923408255778</v>
       </c>
       <c r="C51">
         <v>339.231271826982</v>
@@ -1819,10 +1819,10 @@
     </row>
     <row r="52" spans="1:3">
       <c r="A52">
-        <v>-12.634611745046657</v>
+        <v>-12.638748951531994</v>
       </c>
       <c r="B52">
-        <v>-18.641221416627214</v>
+        <v>-18.63255463775003</v>
       </c>
       <c r="C52">
         <v>339.231271826982</v>
@@ -1830,10 +1830,10 @@
     </row>
     <row r="53" spans="1:3">
       <c r="A53">
-        <v>-11.586121764439772</v>
+        <v>-11.590053151607803</v>
       </c>
       <c r="B53">
-        <v>-17.269744527922445</v>
+        <v>-17.261721338423573</v>
       </c>
       <c r="C53">
         <v>339.231271826982</v>
@@ -1841,10 +1841,10 @@
     </row>
     <row r="54" spans="1:3">
       <c r="A54">
-        <v>-10.578632365700374</v>
+        <v>-10.582332971430349</v>
       </c>
       <c r="B54">
-        <v>-15.877099436427047</v>
+        <v>-15.869713675289068</v>
       </c>
       <c r="C54">
         <v>339.231271826982</v>
@@ -1852,10 +1852,10 @@
     </row>
     <row r="55" spans="1:3">
       <c r="A55">
-        <v>-9.6311101925546136</v>
+        <v>-9.6345441874706275</v>
       </c>
       <c r="B55">
-        <v>-14.453493847925564</v>
+        <v>-14.44673615264097</v>
       </c>
       <c r="C55">
         <v>339.231271826982</v>
@@ -1863,10 +1863,10 @@
     </row>
     <row r="56" spans="1:3">
       <c r="A56">
-        <v>-8.717178369031032</v>
+        <v>-8.720325922702262</v>
       </c>
       <c r="B56">
-        <v>-13.012545887676572</v>
+        <v>-13.006410890264315</v>
       </c>
       <c r="C56">
         <v>339.231271826982</v>
@@ -1874,10 +1874,10 @@
     </row>
     <row r="57" spans="1:3">
       <c r="A57">
-        <v>-7.8376460711809779</v>
+        <v>-7.8404869273313649</v>
       </c>
       <c r="B57">
-        <v>-11.553837785932235</v>
+        <v>-11.548319962299768</v>
       </c>
       <c r="C57">
         <v>339.231271826982</v>
@@ -1885,10 +1885,10 @@
     </row>
     <row r="58" spans="1:3">
       <c r="A58">
-        <v>-7.0129989394386367</v>
+        <v>-7.0155010498198669</v>
       </c>
       <c r="B58">
-        <v>-10.066793005208101</v>
+        <v>-10.06188340147502</v>
       </c>
       <c r="C58">
         <v>339.231271826982</v>
@@ -1896,10 +1896,10 @@
     </row>
     <row r="59" spans="1:3">
       <c r="A59">
-        <v>-6.2231833424116836</v>
+        <v>-6.225326463168452</v>
       </c>
       <c r="B59">
-        <v>-8.5617650409099664</v>
+        <v>-8.5574579257331642</v>
       </c>
       <c r="C59">
         <v>339.231271826982</v>
@@ -1907,10 +1907,10 @@
     </row>
     <row r="60" spans="1:3">
       <c r="A60">
-        <v>-5.4662358834241251</v>
+        <v>-5.4680009143020749</v>
       </c>
       <c r="B60">
-        <v>-7.039767575700437</v>
+        <v>-7.0360575395176284</v>
       </c>
       <c r="C60">
         <v>339.231271826982</v>
@@ -1918,10 +1918,10 @@
     </row>
     <row r="61" spans="1:3">
       <c r="A61">
-        <v>-4.7481606647278669</v>
+        <v>-4.7495250208565158</v>
       </c>
       <c r="B61">
-        <v>-5.4977007498152286</v>
+        <v>-5.4945813925745526</v>
       </c>
       <c r="C61">
         <v>339.231271826982</v>
@@ -1929,10 +1929,10 @@
     </row>
     <row r="62" spans="1:3">
       <c r="A62">
-        <v>-4.0740451396258752</v>
+        <v>-4.0749831789182025</v>
       </c>
       <c r="B62">
-        <v>-3.9329379604526142</v>
+        <v>-3.9304020968828928</v>
       </c>
       <c r="C62">
         <v>339.231271826982</v>
@@ -1940,10 +1940,10 @@
     </row>
     <row r="63" spans="1:3">
       <c r="A63">
-        <v>-3.4315013189186865</v>
+        <v>-3.4319944982623656</v>
       </c>
       <c r="B63">
-        <v>-2.3518750062963836</v>
+        <v>-2.3499175416144693</v>
       </c>
       <c r="C63">
         <v>339.231271826982</v>
@@ -1951,10 +1951,10 @@
     </row>
     <row r="64" spans="1:3">
       <c r="A64">
-        <v>-2.8210533640799773</v>
+        <v>-2.8210827200333157</v>
       </c>
       <c r="B64">
-        <v>-0.75424126786103818</v>
+        <v>-0.75285708081933755</v>
       </c>
       <c r="C64">
         <v>339.231271826982</v>
@@ -1962,10 +1962,10 @@
     </row>
     <row r="65" spans="1:3">
       <c r="A65">
-        <v>-2.2436372701372962</v>
+        <v>-2.2431831264610564</v>
       </c>
       <c r="B65">
-        <v>0.8604465000087711</v>
+        <v>0.8612625974407575</v>
       </c>
       <c r="C65">
         <v>339.231271826982</v>
@@ -1973,10 +1973,10 @@
     </row>
     <row r="66" spans="1:3">
       <c r="A66">
-        <v>-1.7078319836856812</v>
+        <v>-1.7068691207617752</v>
       </c>
       <c r="B66">
-        <v>2.496617524240623</v>
+        <v>2.4968718436985236</v>
       </c>
       <c r="C66">
         <v>339.231271826982</v>
@@ -1984,10 +1984,10 @@
     </row>
     <row r="67" spans="1:3">
       <c r="A67">
-        <v>-1.2024885217635939</v>
+        <v>-1.2009980689144464</v>
       </c>
       <c r="B67">
-        <v>4.1485156930553764</v>
+        <v>4.14821264409109</v>
       </c>
       <c r="C67">
         <v>339.231271826982</v>
@@ -1995,10 +1995,10 @@
     </row>
     <row r="68" spans="1:3">
       <c r="A68">
-        <v>-0.72772747371769142</v>
+        <v>-0.72569011902452485</v>
       </c>
       <c r="B68">
-        <v>5.81620326556322</v>
+        <v>5.8153470857744658</v>
       </c>
       <c r="C68">
         <v>339.231271826982</v>
@@ -2006,10 +2006,10 @@
     </row>
     <row r="69" spans="1:3">
       <c r="A69">
-        <v>-0.28347115476825768</v>
+        <v>-0.28086716529184941</v>
       </c>
       <c r="B69">
-        <v>7.4996401338657872</v>
+        <v>7.4982348071717411</v>
       </c>
       <c r="C69">
         <v>339.231271826982</v>
@@ -2017,10 +2017,10 @@
     </row>
     <row r="70" spans="1:3">
       <c r="A70">
-        <v>0.13059338895845618</v>
+        <v>0.13378414611098666</v>
       </c>
       <c r="B70">
-        <v>9.1986647229131133</v>
+        <v>9.1967138810690372</v>
       </c>
       <c r="C70">
         <v>339.231271826982</v>
@@ -2028,10 +2028,10 @@
     </row>
     <row r="71" spans="1:3">
       <c r="A71">
-        <v>0.51506797532148774</v>
+        <v>0.51886600240592762</v>
       </c>
       <c r="B71">
-        <v>10.912966319981067</v>
+        <v>10.910473124099356</v>
       </c>
       <c r="C71">
         <v>339.231271826982</v>
@@ -2039,10 +2039,10 @@
     </row>
     <row r="72" spans="1:3">
       <c r="A72">
-        <v>0.87091986704142255</v>
+        <v>0.8753459837413623</v>
       </c>
       <c r="B72">
-        <v>12.64204553670762</v>
+        <v>12.639012534207762</v>
       </c>
       <c r="C72">
         <v>339.231271826982</v>
@@ -2050,10 +2050,10 @@
     </row>
     <row r="73" spans="1:3">
       <c r="A73">
-        <v>1.1995907764463398</v>
+        <v>1.204666029862981</v>
       </c>
       <c r="B73">
-        <v>14.385158030999643</v>
+        <v>14.381586981559652</v>
       </c>
       <c r="C73">
         <v>339.231271826982</v>
@@ -2061,10 +2061,10 @@
     </row>
     <row r="74" spans="1:3">
       <c r="A74">
-        <v>1.5031519570210434</v>
+        <v>1.50889746966005</v>
       </c>
       <c r="B74">
-        <v>16.141234434770148</v>
+        <v>16.137126096219479</v>
       </c>
       <c r="C74">
         <v>339.231271826982</v>
@@ -2072,10 +2072,10 @@
     </row>
     <row r="75" spans="1:3">
       <c r="A75">
-        <v>1.7845252050094334</v>
+        <v>1.7909619265363534</v>
       </c>
       <c r="B75">
-        <v>17.908766252954265</v>
+        <v>17.904120114155742</v>
       </c>
       <c r="C75">
         <v>339.231271826982</v>
@@ -2083,10 +2083,10 @@
     </row>
     <row r="76" spans="1:3">
       <c r="A76">
-        <v>2.0477990420384589</v>
+        <v>2.0549473558519771</v>
       </c>
       <c r="B76">
-        <v>19.685642621486885</v>
+        <v>19.680456563255508</v>
       </c>
       <c r="C76">
         <v>339.231271826982</v>
@@ -2094,10 +2094,10 @@
     </row>
     <row r="77" spans="1:3">
       <c r="A77">
-        <v>2.2986845766583519</v>
+        <v>2.3065636909510308</v>
       </c>
       <c r="B77">
-        <v>21.4689149504104</v>
+        <v>21.463184805878758</v>
       </c>
       <c r="C77">
         <v>339.231271826982</v>
@@ -2105,10 +2105,10 @@
     </row>
     <row r="78" spans="1:3">
       <c r="A78">
-        <v>2.5461274351130023</v>
+        <v>2.5547560209077158</v>
       </c>
       <c r="B78">
-        <v>23.253964699650616</v>
+        <v>23.247682420899864</v>
       </c>
       <c r="C78">
         <v>339.231271826982</v>
@@ -2116,10 +2116,10 @@
     </row>
     <row r="79" spans="1:3">
       <c r="A79">
-        <v>2.80653912859926</v>
+        <v>2.8159308513466</v>
       </c>
       <c r="B79">
-        <v>25.032318765137031</v>
+        <v>25.025471261531525</v>
       </c>
       <c r="C79">
         <v>339.231271826982</v>
@@ -2127,10 +2127,10 @@
     </row>
     <row r="80" spans="1:3">
       <c r="A80">
-        <v>3.116639554003457</v>
+        <v>3.12679671341597</v>
       </c>
       <c r="B80">
-        <v>26.78501902022029</v>
+        <v>26.777582004107703</v>
       </c>
       <c r="C80">
         <v>339.231271826982</v>
@@ -2138,10 +2138,10 @@
     </row>
     <row r="81" spans="1:3">
       <c r="A81">
-        <v>3.56868724380857</v>
+        <v>3.5795777940376796</v>
       </c>
       <c r="B81">
-        <v>28.464433279311528</v>
+        <v>28.456357322202226</v>
       </c>
       <c r="C81">
         <v>339.231271826982</v>
@@ -2149,10 +2149,10 @@
     </row>
     <row r="82" spans="1:3">
       <c r="A82">
-        <v>5.1946694610860655</v>
+        <v>5.20584881217977</v>
       </c>
       <c r="B82">
-        <v>29.537756526798326</v>
+        <v>29.528725634967167</v>
       </c>
       <c r="C82">
         <v>339.231271826982</v>
@@ -2170,10 +2170,10 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1">
-        <v>5.1946694610860655</v>
+        <v>5.20584881217977</v>
       </c>
       <c r="B1">
-        <v>29.537756526798326</v>
+        <v>29.528725634967167</v>
       </c>
       <c r="C1">
         <v>353.47999474773957</v>
@@ -2181,10 +2181,10 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2">
-        <v>7.5088519916245273</v>
+        <v>7.5181465469401836</v>
       </c>
       <c r="B2">
-        <v>26.430164432109464</v>
+        <v>26.421081512527248</v>
       </c>
       <c r="C2">
         <v>353.47999474773957</v>
@@ -2192,10 +2192,10 @@
     </row>
     <row r="3" spans="1:3">
       <c r="A3">
-        <v>8.47560497095789</v>
+        <v>8.483591439017566</v>
       </c>
       <c r="B3">
-        <v>24.018237147206882</v>
+        <v>24.009430574891994</v>
       </c>
       <c r="C3">
         <v>353.47999474773957</v>
@@ -2203,10 +2203,10 @@
     </row>
     <row r="4" spans="1:3">
       <c r="A4">
-        <v>9.1437681968685158</v>
+        <v>9.1505929748291024</v>
       </c>
       <c r="B4">
-        <v>21.760468856244419</v>
+        <v>21.752001787909421</v>
       </c>
       <c r="C4">
         <v>353.47999474773957</v>
@@ -2214,10 +2214,10 @@
     </row>
     <row r="5" spans="1:3">
       <c r="A5">
-        <v>9.6116973828171322</v>
+        <v>9.6174640035878074</v>
       </c>
       <c r="B5">
-        <v>19.606079458225427</v>
+        <v>19.597991477367675</v>
       </c>
       <c r="C5">
         <v>353.47999474773957</v>
@@ -2225,10 +2225,10 @@
     </row>
     <row r="6" spans="1:3">
       <c r="A6">
-        <v>9.92837662762563</v>
+        <v>9.9331652747718966</v>
       </c>
       <c r="B6">
-        <v>17.529778937980666</v>
+        <v>17.522098922297211</v>
       </c>
       <c r="C6">
         <v>353.47999474773957</v>
@@ -2236,10 +2236,10 @@
     </row>
     <row r="7" spans="1:3">
       <c r="A7">
-        <v>10.112204465022293</v>
+        <v>10.116086227597757</v>
       </c>
       <c r="B7">
-        <v>15.522068310976943</v>
+        <v>15.51482128470311</v>
       </c>
       <c r="C7">
         <v>353.47999474773957</v>
@@ -2247,10 +2247,10 @@
     </row>
     <row r="8" spans="1:3">
       <c r="A8">
-        <v>10.187887382187222</v>
+        <v>10.190920255360306</v>
       </c>
       <c r="B8">
-        <v>13.570191857489066</v>
+        <v>13.563398125658212</v>
       </c>
       <c r="C8">
         <v>353.47999474773957</v>
@@ -2258,10 +2258,10 @@
     </row>
     <row r="9" spans="1:3">
       <c r="A9">
-        <v>10.163338310614659</v>
+        <v>10.165575946234672</v>
       </c>
       <c r="B9">
-        <v>11.670064207726931</v>
+        <v>11.663742641246829</v>
       </c>
       <c r="C9">
         <v>353.47999474773957</v>
@@ -2269,10 +2269,10 @@
     </row>
     <row r="10" spans="1:3">
       <c r="A10">
-        <v>10.045449656600594</v>
+        <v>10.046941824871954</v>
       </c>
       <c r="B10">
-        <v>9.8181268791631222</v>
+        <v>9.8122951506645038</v>
       </c>
       <c r="C10">
         <v>353.47999474773957</v>
@@ -2280,10 +2280,10 @@
     </row>
     <row r="11" spans="1:3">
       <c r="A11">
-        <v>9.8403415954081179</v>
+        <v>9.8411345768532339</v>
       </c>
       <c r="B11">
-        <v>8.0112200846633623</v>
+        <v>8.00589482494529</v>
       </c>
       <c r="C11">
         <v>353.47999474773957</v>
@@ -2291,10 +2291,10 @@
     </row>
     <row r="12" spans="1:3">
       <c r="A12">
-        <v>9.5535143105951743</v>
+        <v>9.5536512434615037</v>
       </c>
       <c r="B12">
-        <v>6.2465041327979822</v>
+        <v>6.2417010395247887</v>
       </c>
       <c r="C12">
         <v>353.47999474773957</v>
@@ -2302,10 +2302,10 @@
     </row>
     <row r="13" spans="1:3">
       <c r="A13">
-        <v>9.1899441678981955</v>
+        <v>9.18946536332227</v>
       </c>
       <c r="B13">
-        <v>4.5214097741985428</v>
+        <v>4.5171436925492445</v>
       </c>
       <c r="C13">
         <v>353.47999474773957</v>
@@ -2313,10 +2313,10 @@
     </row>
     <row r="14" spans="1:3">
       <c r="A14">
-        <v>8.754148099496355</v>
+        <v>8.75309132977036</v>
       </c>
       <c r="B14">
-        <v>2.8336049605865754</v>
+        <v>2.829889947872803</v>
       </c>
       <c r="C14">
         <v>353.47999474773957</v>
@@ -2324,10 +2324,10 @@
     </row>
     <row r="15" spans="1:3">
       <c r="A15">
-        <v>8.25023115444066</v>
+        <v>8.2486319159401784</v>
       </c>
       <c r="B15">
-        <v>1.1809702949482013</v>
+        <v>1.1778196762208573</v>
       </c>
       <c r="C15">
         <v>353.47999474773957</v>
@@ -2335,10 +2335,10 @@
     </row>
     <row r="16" spans="1:3">
       <c r="A16">
-        <v>7.6819265473345659</v>
+        <v>7.6798182975489659</v>
       </c>
       <c r="B16">
-        <v>-0.43842164521126553</v>
+        <v>-0.44099522679052866</v>
       </c>
       <c r="C16">
         <v>353.47999474773957</v>
@@ -2346,10 +2346,10 @@
     </row>
     <row r="17" spans="1:3">
       <c r="A17">
-        <v>7.0526341102524919</v>
+        <v>7.05004847705497</v>
       </c>
       <c r="B17">
-        <v>-2.0263261602199565</v>
+        <v>-2.0283106965374773</v>
       </c>
       <c r="C17">
         <v>353.47999474773957</v>
@@ -2357,10 +2357,10 @@
     </row>
     <row r="18" spans="1:3">
       <c r="A18">
-        <v>6.36546096986928</v>
+        <v>6.3624279301712425</v>
       </c>
       <c r="B18">
-        <v>-3.5843474294468773</v>
+        <v>-3.5857315036848814</v>
       </c>
       <c r="C18">
         <v>353.47999474773957</v>
@@ -2368,10 +2368,10 @@
     </row>
     <row r="19" spans="1:3">
       <c r="A19">
-        <v>5.6039665383007</v>
+        <v>5.600524561360535</v>
       </c>
       <c r="B19">
-        <v>-5.103997336809794</v>
+        <v>-5.1047662777254681</v>
       </c>
       <c r="C19">
         <v>353.47999474773957</v>
@@ -2379,10 +2379,10 @@
     </row>
     <row r="20" spans="1:3">
       <c r="A20">
-        <v>4.7867603436399371</v>
+        <v>4.7829382923707522</v>
       </c>
       <c r="B20">
-        <v>-6.5948838011862376</v>
+        <v>-6.5950266245928626</v>
       </c>
       <c r="C20">
         <v>353.47999474773957</v>
@@ -2390,10 +2390,10 @@
     </row>
     <row r="21" spans="1:3">
       <c r="A21">
-        <v>3.9171873454579251</v>
+        <v>3.9130123942051256</v>
       </c>
       <c r="B21">
-        <v>-8.0587337927629346</v>
+        <v>-8.0582401969002184</v>
       </c>
       <c r="C21">
         <v>353.47999474773957</v>
@@ -2401,10 +2401,10 @@
     </row>
     <row r="22" spans="1:3">
       <c r="A22">
-        <v>2.9974594888669941</v>
+        <v>2.9929577079965135</v>
       </c>
       <c r="B22">
-        <v>-9.49668931734974</v>
+        <v>-9.495549458257809</v>
       </c>
       <c r="C22">
         <v>353.47999474773957</v>
@@ -2412,10 +2412,10 @@
     </row>
     <row r="23" spans="1:3">
       <c r="A23">
-        <v>2.0105763184140781</v>
+        <v>2.0057827455824944</v>
       </c>
       <c r="B23">
-        <v>-10.899973204668262</v>
+        <v>-10.898173969120981</v>
       </c>
       <c r="C23">
         <v>353.47999474773957</v>
@@ -2423,10 +2423,10 @@
     </row>
     <row r="24" spans="1:3">
       <c r="A24">
-        <v>0.9667489657953976</v>
+        <v>0.96169350605626769</v>
       </c>
       <c r="B24">
-        <v>-12.273857362984742</v>
+        <v>-12.271387732400712</v>
       </c>
       <c r="C24">
         <v>353.47999474773957</v>
@@ -2434,10 +2434,10 @@
     </row>
     <row r="25" spans="1:3">
       <c r="A25">
-        <v>-0.1241719799523807</v>
+        <v>-0.12946446421153307</v>
       </c>
       <c r="B25">
-        <v>-13.623427555886842</v>
+        <v>-13.620278485196037</v>
       </c>
       <c r="C25">
         <v>353.47999474773957</v>
@@ -2445,10 +2445,10 @@
     </row>
     <row r="26" spans="1:3">
       <c r="A26">
-        <v>-1.2642642271431508</v>
+        <v>-1.2697676836310214</v>
       </c>
       <c r="B26">
-        <v>-14.947611082721913</v>
+        <v>-14.943773175859597</v>
       </c>
       <c r="C26">
         <v>353.47999474773957</v>
@@ -2456,10 +2456,10 @@
     </row>
     <row r="27" spans="1:3">
       <c r="A27">
-        <v>-2.4793865113401483</v>
+        <v>-2.4850607319690479</v>
       </c>
       <c r="B27">
-        <v>-16.233057329099168</v>
+        <v>-16.22851648389031</v>
       </c>
       <c r="C27">
         <v>353.47999474773957</v>
@@ -2467,10 +2467,10 @@
     </row>
     <row r="28" spans="1:3">
       <c r="A28">
-        <v>-3.7403634408536677</v>
+        <v>-3.7461835293606622</v>
       </c>
       <c r="B28">
-        <v>-17.494829266802249</v>
+        <v>-17.489577031643311</v>
       </c>
       <c r="C28">
         <v>353.47999474773957</v>
@@ -2478,10 +2478,10 @@
     </row>
     <row r="29" spans="1:3">
       <c r="A29">
-        <v>-5.04588451564527</v>
+        <v>-5.05182620467792</v>
       </c>
       <c r="B29">
-        <v>-18.733603494291639</v>
+        <v>-18.727631701810719</v>
       </c>
       <c r="C29">
         <v>353.47999474773957</v>
@@ -2489,10 +2489,10 @@
     </row>
     <row r="30" spans="1:3">
       <c r="A30">
-        <v>-6.4293605010136785</v>
+        <v>-6.4353806751419222</v>
       </c>
       <c r="B30">
-        <v>-19.93213035746443</v>
+        <v>-19.925425048157468</v>
       </c>
       <c r="C30">
         <v>353.47999474773957</v>
@@ -2500,10 +2500,10 @@
     </row>
     <row r="31" spans="1:3">
       <c r="A31">
-        <v>-7.8651469047797073</v>
+        <v>-7.8712160207440078</v>
       </c>
       <c r="B31">
-        <v>-21.103649858929955</v>
+        <v>-21.096201981397609</v>
       </c>
       <c r="C31">
         <v>353.47999474773957</v>
@@ -2511,10 +2511,10 @@
     </row>
     <row r="32" spans="1:3">
       <c r="A32">
-        <v>-9.3463909710778</v>
+        <v>-9.352483206401363</v>
       </c>
       <c r="B32">
-        <v>-22.251700010082963</v>
+        <v>-22.243501775896583</v>
       </c>
       <c r="C32">
         <v>353.47999474773957</v>
@@ -2522,10 +2522,10 @@
     </row>
     <row r="33" spans="1:3">
       <c r="A33">
-        <v>-10.908943903270341</v>
+        <v>-10.915012177501808</v>
       </c>
       <c r="B33">
-        <v>-23.357771182315837</v>
+        <v>-23.348809121732216</v>
       </c>
       <c r="C33">
         <v>353.47999474773957</v>
@@ -2533,10 +2533,10 @@
     </row>
     <row r="34" spans="1:3">
       <c r="A34">
-        <v>-12.531456630552791</v>
+        <v>-12.537465182555593</v>
       </c>
       <c r="B34">
-        <v>-24.432885693839633</v>
+        <v>-24.423150412542533</v>
       </c>
       <c r="C34">
         <v>353.47999474773957</v>
@@ -2544,10 +2544,10 @@
     </row>
     <row r="35" spans="1:3">
       <c r="A35">
-        <v>-14.202464504244645</v>
+        <v>-14.208384175594929</v>
       </c>
       <c r="B35">
-        <v>-25.482962631582826</v>
+        <v>-25.472446652948104</v>
       </c>
       <c r="C35">
         <v>353.47999474773957</v>
@@ -2555,10 +2555,10 @@
     </row>
     <row r="36" spans="1:3">
       <c r="A36">
-        <v>-15.966791866082131</v>
+        <v>-15.972565016579285</v>
       </c>
       <c r="B36">
-        <v>-26.484859622617762</v>
+        <v>-26.473549350217425</v>
       </c>
       <c r="C36">
         <v>353.47999474773957</v>
@@ -2566,10 +2566,10 @@
     </row>
     <row r="37" spans="1:3">
       <c r="A37">
-        <v>-17.797555204414206</v>
+        <v>-17.803139063072919</v>
       </c>
       <c r="B37">
-        <v>-27.452456363291009</v>
+        <v>-27.440343014541661</v>
       </c>
       <c r="C37">
         <v>353.47999474773957</v>
@@ -2577,10 +2577,10 @@
     </row>
     <row r="38" spans="1:3">
       <c r="A38">
-        <v>-19.682688054455113</v>
+        <v>-19.688047368976878</v>
       </c>
       <c r="B38">
-        <v>-28.391982652349729</v>
+        <v>-28.379059168797564</v>
       </c>
       <c r="C38">
         <v>353.47999474773957</v>
@@ -2588,10 +2588,10 @@
     </row>
     <row r="39" spans="1:3">
       <c r="A39">
-        <v>-21.684247123249055</v>
+        <v>-21.689303160958378</v>
       </c>
       <c r="B39">
-        <v>-29.271399213778889</v>
+        <v>-29.257652156800351</v>
       </c>
       <c r="C39">
         <v>353.47999474773957</v>
@@ -2599,10 +2599,10 @@
     </row>
     <row r="40" spans="1:3">
       <c r="A40">
-        <v>-23.685806192042989</v>
+        <v>-23.690558952939881</v>
       </c>
       <c r="B40">
-        <v>-30.150815775208049</v>
+        <v>-30.136245144803137</v>
       </c>
       <c r="C40">
         <v>353.47999474773957</v>
@@ -2610,10 +2610,10 @@
     </row>
     <row r="41" spans="1:3">
       <c r="A41">
-        <v>-25.68736526083692</v>
+        <v>-25.69181474492137</v>
       </c>
       <c r="B41">
-        <v>-31.030232336637198</v>
+        <v>-31.01483813280592</v>
       </c>
       <c r="C41">
         <v>353.47999474773957</v>
@@ -2621,10 +2621,10 @@
     </row>
     <row r="42" spans="1:3">
       <c r="A42">
-        <v>-25.913292791802302</v>
+        <v>-25.917650762152356</v>
       </c>
       <c r="B42">
-        <v>-30.913588143466615</v>
+        <v>-30.898136200794493</v>
       </c>
       <c r="C42">
         <v>353.47999474773957</v>
@@ -2632,10 +2632,10 @@
     </row>
     <row r="43" spans="1:3">
       <c r="A43">
-        <v>-24.405990618049021</v>
+        <v>-24.410451662544638</v>
       </c>
       <c r="B43">
-        <v>-29.778991540478714</v>
+        <v>-29.764236857188461</v>
       </c>
       <c r="C43">
         <v>353.47999474773957</v>
@@ -2643,10 +2643,10 @@
     </row>
     <row r="44" spans="1:3">
       <c r="A44">
-        <v>-22.898688444295729</v>
+        <v>-22.90325256293691</v>
       </c>
       <c r="B44">
-        <v>-28.6443949374908</v>
+        <v>-28.630337513582425</v>
       </c>
       <c r="C44">
         <v>353.47999474773957</v>
@@ -2654,10 +2654,10 @@
     </row>
     <row r="45" spans="1:3">
       <c r="A45">
-        <v>-21.391386270542437</v>
+        <v>-21.396053463329185</v>
       </c>
       <c r="B45">
-        <v>-27.509798334502889</v>
+        <v>-27.49643816997639</v>
       </c>
       <c r="C45">
         <v>353.47999474773957</v>
@@ -2665,10 +2665,10 @@
     </row>
     <row r="46" spans="1:3">
       <c r="A46">
-        <v>-19.980169997276917</v>
+        <v>-19.984869770540627</v>
       </c>
       <c r="B46">
-        <v>-26.325593512943414</v>
+        <v>-26.312922367419088</v>
       </c>
       <c r="C46">
         <v>353.47999474773957</v>
@@ -2676,10 +2676,10 @@
     </row>
     <row r="47" spans="1:3">
       <c r="A47">
-        <v>-18.613544158376129</v>
+        <v>-18.618245220910968</v>
       </c>
       <c r="B47">
-        <v>-25.11836708256374</v>
+        <v>-25.106380396763452</v>
       </c>
       <c r="C47">
         <v>353.47999474773957</v>
@@ -2687,10 +2687,10 @@
     </row>
     <row r="48" spans="1:3">
       <c r="A48">
-        <v>-17.301348442987607</v>
+        <v>-17.306012886874022</v>
       </c>
       <c r="B48">
-        <v>-23.88303890728324</v>
+        <v>-23.871730966881962</v>
       </c>
       <c r="C48">
         <v>353.47999474773957</v>
@@ -2698,10 +2698,10 @@
     </row>
     <row r="49" spans="1:3">
       <c r="A49">
-        <v>-16.065004676267161</v>
+        <v>-16.06958193666965</v>
       </c>
       <c r="B49">
-        <v>-22.608549106524872</v>
+        <v>-22.597910779160927</v>
       </c>
       <c r="C49">
         <v>353.47999474773957</v>
@@ -2709,10 +2709,10 @@
     </row>
     <row r="50" spans="1:3">
       <c r="A50">
-        <v>-14.86779164701567</v>
+        <v>-14.872256358638323</v>
       </c>
       <c r="B50">
-        <v>-21.313856485504921</v>
+        <v>-21.303882687755713</v>
       </c>
       <c r="C50">
         <v>353.47999474773957</v>
@@ -2720,10 +2720,10 @@
     </row>
     <row r="51" spans="1:3">
       <c r="A51">
-        <v>-13.718855293630323</v>
+        <v>-13.723176427676478</v>
       </c>
       <c r="B51">
-        <v>-19.994239084927113</v>
+        <v>-19.984923408255778</v>
       </c>
       <c r="C51">
         <v>353.47999474773957</v>
@@ -2731,10 +2731,10 @@
     </row>
     <row r="52" spans="1:3">
       <c r="A52">
-        <v>-12.634611745046657</v>
+        <v>-12.638748951531994</v>
       </c>
       <c r="B52">
-        <v>-18.641221416627214</v>
+        <v>-18.63255463775003</v>
       </c>
       <c r="C52">
         <v>353.47999474773957</v>
@@ -2742,10 +2742,10 @@
     </row>
     <row r="53" spans="1:3">
       <c r="A53">
-        <v>-11.586121764439772</v>
+        <v>-11.590053151607803</v>
       </c>
       <c r="B53">
-        <v>-17.269744527922445</v>
+        <v>-17.261721338423573</v>
       </c>
       <c r="C53">
         <v>353.47999474773957</v>
@@ -2753,10 +2753,10 @@
     </row>
     <row r="54" spans="1:3">
       <c r="A54">
-        <v>-10.578632365700374</v>
+        <v>-10.582332971430349</v>
       </c>
       <c r="B54">
-        <v>-15.877099436427047</v>
+        <v>-15.869713675289068</v>
       </c>
       <c r="C54">
         <v>353.47999474773957</v>
@@ -2764,10 +2764,10 @@
     </row>
     <row r="55" spans="1:3">
       <c r="A55">
-        <v>-9.6311101925546136</v>
+        <v>-9.6345441874706275</v>
       </c>
       <c r="B55">
-        <v>-14.453493847925564</v>
+        <v>-14.44673615264097</v>
       </c>
       <c r="C55">
         <v>353.47999474773957</v>
@@ -2775,10 +2775,10 @@
     </row>
     <row r="56" spans="1:3">
       <c r="A56">
-        <v>-8.717178369031032</v>
+        <v>-8.720325922702262</v>
       </c>
       <c r="B56">
-        <v>-13.012545887676572</v>
+        <v>-13.006410890264315</v>
       </c>
       <c r="C56">
         <v>353.47999474773957</v>
@@ -2786,10 +2786,10 @@
     </row>
     <row r="57" spans="1:3">
       <c r="A57">
-        <v>-7.8376460711809779</v>
+        <v>-7.8404869273313649</v>
       </c>
       <c r="B57">
-        <v>-11.553837785932235</v>
+        <v>-11.548319962299768</v>
       </c>
       <c r="C57">
         <v>353.47999474773957</v>
@@ -2797,10 +2797,10 @@
     </row>
     <row r="58" spans="1:3">
       <c r="A58">
-        <v>-7.0129989394386367</v>
+        <v>-7.0155010498198669</v>
       </c>
       <c r="B58">
-        <v>-10.066793005208101</v>
+        <v>-10.06188340147502</v>
       </c>
       <c r="C58">
         <v>353.47999474773957</v>
@@ -2808,10 +2808,10 @@
     </row>
     <row r="59" spans="1:3">
       <c r="A59">
-        <v>-6.2231833424116836</v>
+        <v>-6.225326463168452</v>
       </c>
       <c r="B59">
-        <v>-8.5617650409099664</v>
+        <v>-8.5574579257331642</v>
       </c>
       <c r="C59">
         <v>353.47999474773957</v>
@@ -2819,10 +2819,10 @@
     </row>
     <row r="60" spans="1:3">
       <c r="A60">
-        <v>-5.4662358834241251</v>
+        <v>-5.4680009143020749</v>
       </c>
       <c r="B60">
-        <v>-7.039767575700437</v>
+        <v>-7.0360575395176284</v>
       </c>
       <c r="C60">
         <v>353.47999474773957</v>
@@ -2830,10 +2830,10 @@
     </row>
     <row r="61" spans="1:3">
       <c r="A61">
-        <v>-4.7481606647278669</v>
+        <v>-4.7495250208565158</v>
       </c>
       <c r="B61">
-        <v>-5.4977007498152286</v>
+        <v>-5.4945813925745526</v>
       </c>
       <c r="C61">
         <v>353.47999474773957</v>
@@ -2841,10 +2841,10 @@
     </row>
     <row r="62" spans="1:3">
       <c r="A62">
-        <v>-4.0740451396258752</v>
+        <v>-4.0749831789182025</v>
       </c>
       <c r="B62">
-        <v>-3.9329379604526142</v>
+        <v>-3.9304020968828928</v>
       </c>
       <c r="C62">
         <v>353.47999474773957</v>
@@ -2852,10 +2852,10 @@
     </row>
     <row r="63" spans="1:3">
       <c r="A63">
-        <v>-3.4315013189186865</v>
+        <v>-3.4319944982623656</v>
       </c>
       <c r="B63">
-        <v>-2.3518750062963836</v>
+        <v>-2.3499175416144693</v>
       </c>
       <c r="C63">
         <v>353.47999474773957</v>
@@ -2863,10 +2863,10 @@
     </row>
     <row r="64" spans="1:3">
       <c r="A64">
-        <v>-2.8210533640799773</v>
+        <v>-2.8210827200333157</v>
       </c>
       <c r="B64">
-        <v>-0.75424126786103818</v>
+        <v>-0.75285708081933755</v>
       </c>
       <c r="C64">
         <v>353.47999474773957</v>
@@ -2874,10 +2874,10 @@
     </row>
     <row r="65" spans="1:3">
       <c r="A65">
-        <v>-2.2436372701372962</v>
+        <v>-2.2431831264610564</v>
       </c>
       <c r="B65">
-        <v>0.8604465000087711</v>
+        <v>0.8612625974407575</v>
       </c>
       <c r="C65">
         <v>353.47999474773957</v>
@@ -2885,10 +2885,10 @@
     </row>
     <row r="66" spans="1:3">
       <c r="A66">
-        <v>-1.7078319836856812</v>
+        <v>-1.7068691207617752</v>
       </c>
       <c r="B66">
-        <v>2.496617524240623</v>
+        <v>2.4968718436985236</v>
       </c>
       <c r="C66">
         <v>353.47999474773957</v>
@@ -2896,10 +2896,10 @@
     </row>
     <row r="67" spans="1:3">
       <c r="A67">
-        <v>-1.2024885217635939</v>
+        <v>-1.2009980689144464</v>
       </c>
       <c r="B67">
-        <v>4.1485156930553764</v>
+        <v>4.14821264409109</v>
       </c>
       <c r="C67">
         <v>353.47999474773957</v>
@@ -2907,10 +2907,10 @@
     </row>
     <row r="68" spans="1:3">
       <c r="A68">
-        <v>-0.72772747371769142</v>
+        <v>-0.72569011902452485</v>
       </c>
       <c r="B68">
-        <v>5.81620326556322</v>
+        <v>5.8153470857744658</v>
       </c>
       <c r="C68">
         <v>353.47999474773957</v>
@@ -2918,10 +2918,10 @@
     </row>
     <row r="69" spans="1:3">
       <c r="A69">
-        <v>-0.28347115476825768</v>
+        <v>-0.28086716529184941</v>
       </c>
       <c r="B69">
-        <v>7.4996401338657872</v>
+        <v>7.4982348071717411</v>
       </c>
       <c r="C69">
         <v>353.47999474773957</v>
@@ -2929,10 +2929,10 @@
     </row>
     <row r="70" spans="1:3">
       <c r="A70">
-        <v>0.13059338895845618</v>
+        <v>0.13378414611098666</v>
       </c>
       <c r="B70">
-        <v>9.1986647229131133</v>
+        <v>9.1967138810690372</v>
       </c>
       <c r="C70">
         <v>353.47999474773957</v>
@@ -2940,10 +2940,10 @@
     </row>
     <row r="71" spans="1:3">
       <c r="A71">
-        <v>0.51506797532148774</v>
+        <v>0.51886600240592762</v>
       </c>
       <c r="B71">
-        <v>10.912966319981067</v>
+        <v>10.910473124099356</v>
       </c>
       <c r="C71">
         <v>353.47999474773957</v>
@@ -2951,10 +2951,10 @@
     </row>
     <row r="72" spans="1:3">
       <c r="A72">
-        <v>0.87091986704142255</v>
+        <v>0.8753459837413623</v>
       </c>
       <c r="B72">
-        <v>12.64204553670762</v>
+        <v>12.639012534207762</v>
       </c>
       <c r="C72">
         <v>353.47999474773957</v>
@@ -2962,10 +2962,10 @@
     </row>
     <row r="73" spans="1:3">
       <c r="A73">
-        <v>1.1995907764463398</v>
+        <v>1.204666029862981</v>
       </c>
       <c r="B73">
-        <v>14.385158030999643</v>
+        <v>14.381586981559652</v>
       </c>
       <c r="C73">
         <v>353.47999474773957</v>
@@ -2973,10 +2973,10 @@
     </row>
     <row r="74" spans="1:3">
       <c r="A74">
-        <v>1.5031519570210434</v>
+        <v>1.50889746966005</v>
       </c>
       <c r="B74">
-        <v>16.141234434770148</v>
+        <v>16.137126096219479</v>
       </c>
       <c r="C74">
         <v>353.47999474773957</v>
@@ -2984,10 +2984,10 @@
     </row>
     <row r="75" spans="1:3">
       <c r="A75">
-        <v>1.7845252050094334</v>
+        <v>1.7909619265363534</v>
       </c>
       <c r="B75">
-        <v>17.908766252954265</v>
+        <v>17.904120114155742</v>
       </c>
       <c r="C75">
         <v>353.47999474773957</v>
@@ -2995,10 +2995,10 @@
     </row>
     <row r="76" spans="1:3">
       <c r="A76">
-        <v>2.0477990420384589</v>
+        <v>2.0549473558519771</v>
       </c>
       <c r="B76">
-        <v>19.685642621486885</v>
+        <v>19.680456563255508</v>
       </c>
       <c r="C76">
         <v>353.47999474773957</v>
@@ -3006,10 +3006,10 @@
     </row>
     <row r="77" spans="1:3">
       <c r="A77">
-        <v>2.2986845766583519</v>
+        <v>2.3065636909510308</v>
       </c>
       <c r="B77">
-        <v>21.4689149504104</v>
+        <v>21.463184805878758</v>
       </c>
       <c r="C77">
         <v>353.47999474773957</v>
@@ -3017,10 +3017,10 @@
     </row>
     <row r="78" spans="1:3">
       <c r="A78">
-        <v>2.5461274351130023</v>
+        <v>2.5547560209077158</v>
       </c>
       <c r="B78">
-        <v>23.253964699650616</v>
+        <v>23.247682420899864</v>
       </c>
       <c r="C78">
         <v>353.47999474773957</v>
@@ -3028,10 +3028,10 @@
     </row>
     <row r="79" spans="1:3">
       <c r="A79">
-        <v>2.80653912859926</v>
+        <v>2.8159308513466</v>
       </c>
       <c r="B79">
-        <v>25.032318765137031</v>
+        <v>25.025471261531525</v>
       </c>
       <c r="C79">
         <v>353.47999474773957</v>
@@ -3039,10 +3039,10 @@
     </row>
     <row r="80" spans="1:3">
       <c r="A80">
-        <v>3.116639554003457</v>
+        <v>3.12679671341597</v>
       </c>
       <c r="B80">
-        <v>26.78501902022029</v>
+        <v>26.777582004107703</v>
       </c>
       <c r="C80">
         <v>353.47999474773957</v>
@@ -3050,10 +3050,10 @@
     </row>
     <row r="81" spans="1:3">
       <c r="A81">
-        <v>3.56868724380857</v>
+        <v>3.5795777940376796</v>
       </c>
       <c r="B81">
-        <v>28.464433279311528</v>
+        <v>28.456357322202226</v>
       </c>
       <c r="C81">
         <v>353.47999474773957</v>
@@ -3061,10 +3061,10 @@
     </row>
     <row r="82" spans="1:3">
       <c r="A82">
-        <v>5.1946694610860655</v>
+        <v>5.20584881217977</v>
       </c>
       <c r="B82">
-        <v>29.537756526798326</v>
+        <v>29.528725634967167</v>
       </c>
       <c r="C82">
         <v>353.47999474773957</v>
